--- a/src/main/resources/2012/02/Kozlowski_Maciej.xlsx
+++ b/src/main/resources/2012/02/Kozlowski_Maciej.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Projekt1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dokumentacja techniczna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5</t>
   </si>
   <si>
     <t xml:space="preserve">Budowa produktu, paczak, instalka</t>
@@ -81,10 +84,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -166,7 +170,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -184,6 +188,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,7 +355,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -350,7 +366,7 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -361,8 +377,8 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>2.5</v>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -371,9 +387,9 @@
         <v>40944</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -382,9 +398,9 @@
         <v>40945</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -393,23 +409,24 @@
         <v>40946</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>40948</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -418,9 +435,9 @@
         <v>40951</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -431,7 +448,7 @@
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -440,9 +457,9 @@
         <v>40958</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -451,9 +468,9 @@
         <v>40959</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -496,9 +513,9 @@
         <v>40940</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -507,9 +524,9 @@
         <v>40941</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -518,7 +535,7 @@
         <v>40942</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6</v>
@@ -540,7 +557,7 @@
         <v>40947</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>2</v>
@@ -551,7 +568,7 @@
         <v>40949</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>8</v>
@@ -562,14 +579,14 @@
         <v>40957</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>7</v>
       </c>
     </row>
